--- a/港岛-黄泥涌-Eight Kwai Fong Happy Valley/Eight Kwai Fong Happy Valley_销控明细表.xlsx
+++ b/港岛-黄泥涌-Eight Kwai Fong Happy Valley/Eight Kwai Fong Happy Valley_销控明细表.xlsx
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>16520000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>38779</v>
+        <v>38598</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>15941800</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>37422</v>
+        <v>37247</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>16122000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>40610</v>
+        <v>40508</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>15557730</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>39188</v>
+        <v>39090</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>17156000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>41844</v>
+        <v>41742</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>16555540</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>40379</v>
+        <v>40281</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>16620000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>40537</v>
+        <v>40438</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>16038300</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>39118</v>
+        <v>39023</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>16374000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>39937</v>
+        <v>39839</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>15800910</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>38539</v>
+        <v>38445</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>15564000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>38813</v>
+        <v>38716</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>15019260</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>37455</v>
+        <v>37361</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>15659000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>38193</v>
+        <v>38100</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>15110935</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>36856</v>
+        <v>36766</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>13784000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>34374</v>
+        <v>34289</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>13784000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>34374</v>
+        <v>34289</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>13868000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>33824</v>
+        <v>33742</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>13868000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>33824</v>
+        <v>33742</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>14304000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>33577</v>
+        <v>33421</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>13803360</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>32402</v>
+        <v>32251</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>14535000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>35451</v>
+        <v>35365</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>14535000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>35451</v>
+        <v>35365</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>14120000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>33146</v>
+        <v>32991</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>13625800</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>31985</v>
+        <v>31836</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>14234000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>35496</v>
+        <v>35408</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>13735810</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>34254</v>
+        <v>34169</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>14321000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>34929</v>
+        <v>34844</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>14321000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>34929</v>
+        <v>34844</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>13939000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>32721</v>
+        <v>32568</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>13939000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>32721</v>
+        <v>32568</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>14518000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>35410</v>
+        <v>35324</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>14009870</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>34170</v>
+        <v>34087</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>13761000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>32303</v>
+        <v>32152</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>13761000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>32303</v>
+        <v>32152</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>13955000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>34800</v>
+        <v>34714</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>13466575</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>33582</v>
+        <v>33499</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>13901000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>33905</v>
+        <v>33822</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>13901000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>33905</v>
+        <v>33822</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>13584000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>31887</v>
+        <v>31738</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>13584000</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>31887</v>
+        <v>31738</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>13748000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>34284</v>
+        <v>34199</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>13748000</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>34284</v>
+        <v>34199</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>13410000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>31479</v>
+        <v>31332</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>13410000</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>31479</v>
+        <v>31332</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>12732000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>31751</v>
+        <v>31672</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>12732000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>31751</v>
+        <v>31672</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>12683000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>30934</v>
+        <v>30859</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>12683000</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>30934</v>
+        <v>30859</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>12791000</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>32219</v>
+        <v>32138</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>12343315</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>31091</v>
+        <v>31013</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>13345000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>33279</v>
+        <v>33197</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>12877925</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>32115</v>
+        <v>32035</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>13293000</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>32422</v>
+        <v>32343</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>12827745</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>31287</v>
+        <v>31211</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>13124000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>32010</v>
+        <v>31932</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>13124000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>32010</v>
+        <v>31932</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>12424000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>29164</v>
+        <v>29028</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>12424000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>29164</v>
+        <v>29028</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>12989000</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>32392</v>
+        <v>32311</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>12989000</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>32392</v>
+        <v>32311</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>12930000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>31537</v>
+        <v>31460</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>12930000</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>31537</v>
+        <v>31460</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>12060000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>28310</v>
+        <v>28178</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>12060000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>28310</v>
+        <v>28178</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>12022000</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>30282</v>
+        <v>30206</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>12022000</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>30282</v>
+        <v>30206</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>9383000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>36368</v>
+        <v>36228</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>9054595</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>35095</v>
+        <v>34960</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>12802000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>31925</v>
+        <v>31846</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>12802000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>31925</v>
+        <v>31846</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>12739000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>31071</v>
+        <v>30995</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>12739000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>31071</v>
+        <v>30995</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>11543000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>29076</v>
+        <v>29003</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>11543000</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>29076</v>
+        <v>29003</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>9337000</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>36190</v>
+        <v>36050</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>9010205</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>34923</v>
+        <v>34788</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>12812000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>31249</v>
+        <v>31173</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>12812000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>31249</v>
+        <v>31173</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>8977000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>34795</v>
+        <v>34660</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>8662805</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>33577</v>
+        <v>33447</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 395呎 (1房)
+          <t>B | 396呎 (1房)
 -
 -
 (待售)</t>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 -
 -
 (待售)</t>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 -
 -
 (待售)</t>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 -
 -
 (待售)</t>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 -
 -
 (待售)</t>
@@ -11457,9 +11457,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1716万
-$41,844/呎
+$41,742/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11489,17 +11489,17 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 $1612万
-$40,610/呎
+$40,508/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1652万
-$38,779/呎
+$38,598/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 -
 -
 (待售)</t>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 -
 -
 (待售)</t>
@@ -11567,9 +11567,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1662万
-$40,537/呎
+$40,438/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 -
 -
 (待售)</t>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 -
 -
 (待售)</t>
@@ -11622,9 +11622,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1637万
-$39,937/呎
+$39,839/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 -
 -
 (待售)</t>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 -
 -
 (待售)</t>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 -
 -
 (待售)</t>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -11787,17 +11787,17 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1566万
-$38,193/呎
+$38,100/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1556万
-$38,813/呎
+$38,716/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 -
 -
 (待售)</t>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 -
 -
 (待售)</t>
@@ -12007,17 +12007,17 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1387万
-$33,824/呎
+$33,742/呎
 (21年-12月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1378万
-$34,374/呎
+$34,289/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 -
 -
 (待售)</t>
@@ -12062,9 +12062,9 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1454万
-$35,451/呎
+$35,365/呎
 (20年-11月-13日)</t>
         </is>
       </c>
@@ -12102,9 +12102,9 @@
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1430万
-$33,577/呎
+$33,421/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -12117,17 +12117,17 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1432万
-$34,929/呎
+$34,844/呎
 (20年-11月-12日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1423万
-$35,496/呎
+$35,408/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -12157,9 +12157,9 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1412万
-$33,146/呎
+$32,991/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -12172,9 +12172,9 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1452万
-$35,410/呎
+$35,324/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -12212,9 +12212,9 @@
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1394万
-$32,721/呎
+$32,568/呎
 (21年-06月-18日)</t>
         </is>
       </c>
@@ -12227,17 +12227,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1390万
-$33,905/呎
+$33,822/呎
 (20年-11月-26日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1396万
-$34,800/呎
+$34,714/呎
 (在售)</t>
         </is>
       </c>
@@ -12267,9 +12267,9 @@
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1376万
-$32,303/呎
+$32,152/呎
 (20年-11月-19日)</t>
         </is>
       </c>
@@ -12290,9 +12290,9 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1375万
-$34,284/呎
+$34,199/呎
 (21年-03月-03日)</t>
         </is>
       </c>
@@ -12322,9 +12322,9 @@
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1358万
-$31,887/呎
+$31,738/呎
 (20年-12月-21日)</t>
         </is>
       </c>
@@ -12337,17 +12337,17 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1268万
-$30,934/呎
+$30,859/呎
 (20年-10月-26日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1273万
-$31,751/呎
+$31,672/呎
 (20年-11月-16日)</t>
         </is>
       </c>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -12377,9 +12377,9 @@
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1341万
-$31,479/呎
+$31,332/呎
 (21年-03月-30日)</t>
         </is>
       </c>
@@ -12392,17 +12392,17 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1329万
-$32,422/呎
+$32,343/呎
 (在售)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1334万
-$33,279/呎
+$33,197/呎
 (在售)</t>
         </is>
       </c>
@@ -12424,9 +12424,9 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 $1279万
-$32,219/呎
+$32,138/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -12447,9 +12447,9 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1312万
-$32,010/呎
+$31,932/呎
 (20年-11月-19日)</t>
         </is>
       </c>
@@ -12502,17 +12502,17 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1293万
-$31,537/呎
+$31,460/呎
 (20年-11月-12日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1299万
-$32,392/呎
+$32,311/呎
 (20年-11月-12日)</t>
         </is>
       </c>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 -
 -
 (待售)</t>
@@ -12542,9 +12542,9 @@
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1242万
-$29,164/呎
+$29,028/呎
 (20年-11月-24日)</t>
         </is>
       </c>
@@ -12557,17 +12557,17 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1274万
-$31,071/呎
+$30,995/呎
 (20年-11月-12日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 402呎 (1房)
 $1280万
-$31,925/呎
+$31,846/呎
 (20年-11月-12日)</t>
         </is>
       </c>
@@ -12581,25 +12581,25 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 $938万
-$36,368/呎
+$36,228/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 $1202万
-$30,282/呎
+$30,206/呎
 (22年-04月-29日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 $1206万
-$28,310/呎
+$28,178/呎
 (20年-12月-02日)</t>
         </is>
       </c>
@@ -12612,9 +12612,9 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 $1281万
-$31,249/呎
+$31,173/呎
 (21年-03月-11日)</t>
         </is>
       </c>
@@ -12636,17 +12636,17 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 $934万
-$36,190/呎
+$36,050/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 398呎 (1房)
 $1154万
-$29,076/呎
+$29,003/呎
 (21年-01月-13日)</t>
         </is>
       </c>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 410呎 (1房)
+          <t>A | 411呎 (1房)
 -
 -
 (待售)</t>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 401呎 (1房)
+          <t>B | 386呎 (1房)
 -
 -
 (待售)</t>
@@ -12691,15 +12691,15 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>D | 258呎 (开放式)
+          <t>D | 259呎 (开放式)
 $898万
-$34,795/呎
+$34,660/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>E | 397呎 (1房)
+          <t>E | 382呎 (1房)
 -
 -
 (待售)</t>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 426呎 (1房)
+          <t>F | 428呎 (1房)
 -
 -
 (待售)</t>
